--- a/work/produtos.xlsx
+++ b/work/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca00acb247e603aa/Documents/eclipse-workspace/Maino_API/work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EC05FE9-FA74-4322-AEEC-B2A2B9DB3CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{1EC05FE9-FA74-4322-AEEC-B2A2B9DB3CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72C6F2E-4B2B-4824-9239-85A5DED6663A}"/>
   <bookViews>
-    <workbookView xWindow="6312" yWindow="2220" windowWidth="23040" windowHeight="13560" xr2:uid="{454A413A-3B85-4E3B-9FD2-E6AA5F74B694}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{454A413A-3B85-4E3B-9FD2-E6AA5F74B694}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="877">
   <si>
     <t>Código</t>
   </si>
@@ -2658,6 +2658,18 @@
   </si>
   <si>
     <t>FLUIDO DA MECATRONICA DQ-200 AMBAR</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Nacional, exceto as indicadas nos codigos 3, 4, 5 e 8</t>
+  </si>
+  <si>
+    <t>Estrangeira - Importacao direta, exceto a indicada no codigo 6</t>
+  </si>
+  <si>
+    <t>Estrangeira - Adquirida no mercado interno, exceto a indicada no codigo 7</t>
   </si>
 </sst>
 </file>
@@ -2733,7 +2745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2742,6 +2754,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3076,16 +3091,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BAC720-32A6-4B09-979E-3BD0D8A97F64}">
-  <dimension ref="A1:D436"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="110.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3098,8 +3114,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -3112,8 +3131,11 @@
       <c r="D2" s="5">
         <v>711.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3126,8 +3148,11 @@
       <c r="D3" s="5">
         <v>382.98</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -3140,8 +3165,11 @@
       <c r="D4" s="5">
         <v>955.32</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3154,8 +3182,11 @@
       <c r="D5" s="5">
         <v>957</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3168,8 +3199,11 @@
       <c r="D6" s="5">
         <v>1590</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -3182,8 +3216,11 @@
       <c r="D7" s="5">
         <v>510</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -3196,8 +3233,11 @@
       <c r="D8" s="5">
         <v>480</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -3210,8 +3250,11 @@
       <c r="D9" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -3224,8 +3267,11 @@
       <c r="D10" s="5">
         <v>4700</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -3238,8 +3284,11 @@
       <c r="D11" s="5">
         <v>1008.51</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -3252,8 +3301,11 @@
       <c r="D12" s="5">
         <v>5723.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
@@ -3266,8 +3318,11 @@
       <c r="D13" s="5">
         <v>4700</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -3280,8 +3335,11 @@
       <c r="D14" s="5">
         <v>710</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -3294,8 +3352,11 @@
       <c r="D15" s="5">
         <v>6053.19</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -3308,8 +3369,11 @@
       <c r="D16" s="5">
         <v>4250</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -3322,8 +3386,11 @@
       <c r="D17" s="5">
         <v>5000</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
@@ -3336,8 +3403,11 @@
       <c r="D18" s="5">
         <v>3750</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>39</v>
       </c>
@@ -3350,8 +3420,11 @@
       <c r="D19" s="5">
         <v>6580</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -3364,8 +3437,11 @@
       <c r="D20" s="5">
         <v>3150</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>43</v>
       </c>
@@ -3378,8 +3454,11 @@
       <c r="D21" s="5">
         <v>1500</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
@@ -3392,8 +3471,11 @@
       <c r="D22" s="5">
         <v>3300</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>47</v>
       </c>
@@ -3406,8 +3488,11 @@
       <c r="D23" s="5">
         <v>1148</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
@@ -3420,8 +3505,11 @@
       <c r="D24" s="5">
         <v>130</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>51</v>
       </c>
@@ -3434,8 +3522,11 @@
       <c r="D25" s="5">
         <v>289</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>53</v>
       </c>
@@ -3448,8 +3539,11 @@
       <c r="D26" s="5">
         <v>798</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>55</v>
       </c>
@@ -3462,8 +3556,11 @@
       <c r="D27" s="5">
         <v>420</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>57</v>
       </c>
@@ -3476,8 +3573,11 @@
       <c r="D28" s="5">
         <v>480</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>59</v>
       </c>
@@ -3490,8 +3590,11 @@
       <c r="D29" s="5">
         <v>890</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3504,8 +3607,11 @@
       <c r="D30" s="5">
         <v>1400</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
@@ -3518,8 +3624,11 @@
       <c r="D31" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>65</v>
       </c>
@@ -3532,8 +3641,11 @@
       <c r="D32" s="5">
         <v>11700</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>67</v>
       </c>
@@ -3546,8 +3658,11 @@
       <c r="D33" s="5">
         <v>39900</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>69</v>
       </c>
@@ -3560,8 +3675,11 @@
       <c r="D34" s="5">
         <v>15000</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>71</v>
       </c>
@@ -3574,8 +3692,11 @@
       <c r="D35" s="5">
         <v>14800</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>73</v>
       </c>
@@ -3588,8 +3709,11 @@
       <c r="D36" s="5">
         <v>11600</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>75</v>
       </c>
@@ -3602,8 +3726,11 @@
       <c r="D37" s="5">
         <v>6900</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>77</v>
       </c>
@@ -3616,8 +3743,11 @@
       <c r="D38" s="5">
         <v>8450</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>79</v>
       </c>
@@ -3630,8 +3760,11 @@
       <c r="D39" s="5">
         <v>10500</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>81</v>
       </c>
@@ -3644,8 +3777,11 @@
       <c r="D40" s="5">
         <v>8450</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>83</v>
       </c>
@@ -3658,8 +3794,11 @@
       <c r="D41" s="5">
         <v>12000</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>85</v>
       </c>
@@ -3672,8 +3811,11 @@
       <c r="D42" s="5">
         <v>11900</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>87</v>
       </c>
@@ -3686,8 +3828,11 @@
       <c r="D43" s="5">
         <v>5900</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>89</v>
       </c>
@@ -3700,8 +3845,11 @@
       <c r="D44" s="5">
         <v>5500</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>91</v>
       </c>
@@ -3714,8 +3862,11 @@
       <c r="D45" s="5">
         <v>9500</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>93</v>
       </c>
@@ -3728,8 +3879,11 @@
       <c r="D46" s="5">
         <v>5900</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>95</v>
       </c>
@@ -3742,8 +3896,11 @@
       <c r="D47" s="5">
         <v>7234.04</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>97</v>
       </c>
@@ -3756,8 +3913,11 @@
       <c r="D48" s="5">
         <v>5200</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>99</v>
       </c>
@@ -3770,8 +3930,11 @@
       <c r="D49" s="5">
         <v>5800</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>101</v>
       </c>
@@ -3784,8 +3947,11 @@
       <c r="D50" s="5">
         <v>4000</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>103</v>
       </c>
@@ -3798,8 +3964,11 @@
       <c r="D51" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>105</v>
       </c>
@@ -3812,8 +3981,11 @@
       <c r="D52" s="5">
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>107</v>
       </c>
@@ -3826,8 +3998,11 @@
       <c r="D53" s="5">
         <v>318</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>109</v>
       </c>
@@ -3840,8 +4015,11 @@
       <c r="D54" s="5">
         <v>180</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>111</v>
       </c>
@@ -3854,8 +4032,11 @@
       <c r="D55" s="5">
         <v>2700</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>113</v>
       </c>
@@ -3868,8 +4049,11 @@
       <c r="D56" s="5">
         <v>2700</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>115</v>
       </c>
@@ -3882,8 +4066,11 @@
       <c r="D57" s="5">
         <v>690</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>117</v>
       </c>
@@ -3896,8 +4083,11 @@
       <c r="D58" s="5">
         <v>270</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>119</v>
       </c>
@@ -3910,8 +4100,11 @@
       <c r="D59" s="5">
         <v>290</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>121</v>
       </c>
@@ -3924,8 +4117,11 @@
       <c r="D60" s="5">
         <v>490</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>123</v>
       </c>
@@ -3938,8 +4134,11 @@
       <c r="D61" s="5">
         <v>420</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>125</v>
       </c>
@@ -3952,8 +4151,11 @@
       <c r="D62" s="5">
         <v>470</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>127</v>
       </c>
@@ -3966,8 +4168,11 @@
       <c r="D63" s="5">
         <v>230</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>129</v>
       </c>
@@ -3980,8 +4185,11 @@
       <c r="D64" s="5">
         <v>199</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>131</v>
       </c>
@@ -3994,8 +4202,11 @@
       <c r="D65" s="5">
         <v>735</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>133</v>
       </c>
@@ -4008,8 +4219,11 @@
       <c r="D66" s="5">
         <v>3100</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>135</v>
       </c>
@@ -4022,8 +4236,11 @@
       <c r="D67" s="5">
         <v>1590</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>137</v>
       </c>
@@ -4036,8 +4253,11 @@
       <c r="D68" s="5">
         <v>470</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>139</v>
       </c>
@@ -4050,8 +4270,11 @@
       <c r="D69" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -4064,8 +4287,11 @@
       <c r="D70" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>143</v>
       </c>
@@ -4078,8 +4304,11 @@
       <c r="D71" s="5">
         <v>60</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>145</v>
       </c>
@@ -4092,8 +4321,11 @@
       <c r="D72" s="5">
         <v>69</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>147</v>
       </c>
@@ -4106,8 +4338,11 @@
       <c r="D73" s="5">
         <v>389</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>149</v>
       </c>
@@ -4120,8 +4355,11 @@
       <c r="D74" s="5">
         <v>815</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>151</v>
       </c>
@@ -4134,8 +4372,11 @@
       <c r="D75" s="5">
         <v>840</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>153</v>
       </c>
@@ -4148,8 +4389,11 @@
       <c r="D76" s="5">
         <v>430</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>155</v>
       </c>
@@ -4162,8 +4406,11 @@
       <c r="D77" s="5">
         <v>620</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>157</v>
       </c>
@@ -4176,8 +4423,11 @@
       <c r="D78" s="5">
         <v>230</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>159</v>
       </c>
@@ -4190,8 +4440,11 @@
       <c r="D79" s="5">
         <v>2900</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>161</v>
       </c>
@@ -4204,8 +4457,11 @@
       <c r="D80" s="5">
         <v>230</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>163</v>
       </c>
@@ -4218,8 +4474,11 @@
       <c r="D81" s="5">
         <v>1690</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>165</v>
       </c>
@@ -4232,8 +4491,11 @@
       <c r="D82" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>167</v>
       </c>
@@ -4246,8 +4508,11 @@
       <c r="D83" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>169</v>
       </c>
@@ -4260,8 +4525,11 @@
       <c r="D84" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>171</v>
       </c>
@@ -4274,8 +4542,11 @@
       <c r="D85" s="5">
         <v>400</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E85" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>173</v>
       </c>
@@ -4288,8 +4559,11 @@
       <c r="D86" s="5">
         <v>700</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E86" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>175</v>
       </c>
@@ -4302,8 +4576,11 @@
       <c r="D87" s="5">
         <v>138</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E87" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>177</v>
       </c>
@@ -4316,8 +4593,11 @@
       <c r="D88" s="5">
         <v>905</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E88" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>179</v>
       </c>
@@ -4330,8 +4610,11 @@
       <c r="D89" s="5">
         <v>950</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E89" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>181</v>
       </c>
@@ -4344,8 +4627,11 @@
       <c r="D90" s="5">
         <v>960</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E90" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>183</v>
       </c>
@@ -4358,8 +4644,11 @@
       <c r="D91" s="5">
         <v>980</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>185</v>
       </c>
@@ -4372,8 +4661,11 @@
       <c r="D92" s="5">
         <v>850</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E92" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>187</v>
       </c>
@@ -4386,8 +4678,11 @@
       <c r="D93" s="5">
         <v>850</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E93" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>189</v>
       </c>
@@ -4400,8 +4695,11 @@
       <c r="D94" s="5">
         <v>950</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E94" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>191</v>
       </c>
@@ -4414,8 +4712,11 @@
       <c r="D95" s="5">
         <v>950</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E95" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>193</v>
       </c>
@@ -4428,8 +4729,11 @@
       <c r="D96" s="5">
         <v>2990</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>195</v>
       </c>
@@ -4442,8 +4746,11 @@
       <c r="D97" s="5">
         <v>4100</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>197</v>
       </c>
@@ -4456,8 +4763,11 @@
       <c r="D98" s="5">
         <v>500</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>199</v>
       </c>
@@ -4470,8 +4780,11 @@
       <c r="D99" s="5">
         <v>680</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>201</v>
       </c>
@@ -4484,8 +4797,11 @@
       <c r="D100" s="5">
         <v>160</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E100" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
@@ -4498,8 +4814,11 @@
       <c r="D101" s="5">
         <v>390</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E101" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>205</v>
       </c>
@@ -4512,8 +4831,11 @@
       <c r="D102" s="5">
         <v>230</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E102" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>207</v>
       </c>
@@ -4526,8 +4848,11 @@
       <c r="D103" s="5">
         <v>849</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E103" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>209</v>
       </c>
@@ -4540,8 +4865,11 @@
       <c r="D104" s="5">
         <v>4500</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>211</v>
       </c>
@@ -4554,8 +4882,11 @@
       <c r="D105" s="5">
         <v>4800</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>213</v>
       </c>
@@ -4568,8 +4899,11 @@
       <c r="D106" s="5">
         <v>6300</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>215</v>
       </c>
@@ -4582,8 +4916,11 @@
       <c r="D107" s="5">
         <v>9500</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>217</v>
       </c>
@@ -4596,8 +4933,11 @@
       <c r="D108" s="5">
         <v>6900</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>219</v>
       </c>
@@ -4610,8 +4950,11 @@
       <c r="D109" s="5">
         <v>14900</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E109" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>221</v>
       </c>
@@ -4624,8 +4967,11 @@
       <c r="D110" s="5">
         <v>5200</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>223</v>
       </c>
@@ -4638,8 +4984,11 @@
       <c r="D111" s="5">
         <v>3170.21</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>225</v>
       </c>
@@ -4652,8 +5001,11 @@
       <c r="D112" s="5">
         <v>6900</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>227</v>
       </c>
@@ -4666,8 +5018,11 @@
       <c r="D113" s="5">
         <v>7110.64</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>229</v>
       </c>
@@ -4680,8 +5035,11 @@
       <c r="D114" s="5">
         <v>3569.15</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E114" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>231</v>
       </c>
@@ -4694,8 +5052,11 @@
       <c r="D115" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E115" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>233</v>
       </c>
@@ -4708,8 +5069,11 @@
       <c r="D116" s="5">
         <v>2980</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E116" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>235</v>
       </c>
@@ -4722,8 +5086,11 @@
       <c r="D117" s="5">
         <v>2880</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E117" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>237</v>
       </c>
@@ -4736,8 +5103,11 @@
       <c r="D118" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E118" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>239</v>
       </c>
@@ -4750,8 +5120,11 @@
       <c r="D119" s="5">
         <v>105</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E119" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>241</v>
       </c>
@@ -4764,8 +5137,11 @@
       <c r="D120" s="5">
         <v>1800</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E120" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>243</v>
       </c>
@@ -4778,8 +5154,11 @@
       <c r="D121" s="5">
         <v>590</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E121" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>245</v>
       </c>
@@ -4792,8 +5171,11 @@
       <c r="D122" s="5">
         <v>820</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E122" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>247</v>
       </c>
@@ -4806,8 +5188,11 @@
       <c r="D123" s="5">
         <v>63</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E123" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>249</v>
       </c>
@@ -4820,8 +5205,11 @@
       <c r="D124" s="5">
         <v>950</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E124" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>251</v>
       </c>
@@ -4834,8 +5222,11 @@
       <c r="D125" s="5">
         <v>741</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E125" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>253</v>
       </c>
@@ -4848,8 +5239,11 @@
       <c r="D126" s="5">
         <v>1062</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E126" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>255</v>
       </c>
@@ -4862,8 +5256,11 @@
       <c r="D127" s="5">
         <v>189</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E127" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>257</v>
       </c>
@@ -4876,8 +5273,11 @@
       <c r="D128" s="5">
         <v>270</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E128" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>259</v>
       </c>
@@ -4890,8 +5290,11 @@
       <c r="D129" s="5">
         <v>1900</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E129" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>261</v>
       </c>
@@ -4904,8 +5307,11 @@
       <c r="D130" s="5">
         <v>862</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E130" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>263</v>
       </c>
@@ -4918,8 +5324,11 @@
       <c r="D131" s="5">
         <v>205</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E131" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>265</v>
       </c>
@@ -4932,8 +5341,11 @@
       <c r="D132" s="5">
         <v>205</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E132" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>267</v>
       </c>
@@ -4946,8 +5358,11 @@
       <c r="D133" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E133" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>269</v>
       </c>
@@ -4960,8 +5375,11 @@
       <c r="D134" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E134" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>271</v>
       </c>
@@ -4974,8 +5392,11 @@
       <c r="D135" s="5">
         <v>1062</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E135" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>273</v>
       </c>
@@ -4988,8 +5409,11 @@
       <c r="D136" s="5">
         <v>590</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E136" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
@@ -5002,8 +5426,11 @@
       <c r="D137" s="5">
         <v>1695</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E137" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>277</v>
       </c>
@@ -5016,8 +5443,11 @@
       <c r="D138" s="5">
         <v>1062</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E138" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>279</v>
       </c>
@@ -5030,8 +5460,11 @@
       <c r="D139" s="5">
         <v>1575</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E139" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>281</v>
       </c>
@@ -5044,8 +5477,11 @@
       <c r="D140" s="5">
         <v>734</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E140" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>283</v>
       </c>
@@ -5058,8 +5494,11 @@
       <c r="D141" s="5">
         <v>1130</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E141" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>285</v>
       </c>
@@ -5072,8 +5511,11 @@
       <c r="D142" s="5">
         <v>404</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E142" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>287</v>
       </c>
@@ -5086,8 +5528,11 @@
       <c r="D143" s="5">
         <v>141</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E143" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>289</v>
       </c>
@@ -5100,8 +5545,11 @@
       <c r="D144" s="5">
         <v>580</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E144" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>291</v>
       </c>
@@ -5114,8 +5562,11 @@
       <c r="D145" s="5">
         <v>466</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E145" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>293</v>
       </c>
@@ -5128,8 +5579,11 @@
       <c r="D146" s="5">
         <v>287</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E146" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>295</v>
       </c>
@@ -5142,8 +5596,11 @@
       <c r="D147" s="5">
         <v>390</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E147" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>297</v>
       </c>
@@ -5156,8 +5613,11 @@
       <c r="D148" s="5">
         <v>1580</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E148" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>299</v>
       </c>
@@ -5170,8 +5630,11 @@
       <c r="D149" s="5">
         <v>930</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E149" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>301</v>
       </c>
@@ -5184,8 +5647,11 @@
       <c r="D150" s="5">
         <v>130</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E150" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>303</v>
       </c>
@@ -5198,8 +5664,11 @@
       <c r="D151" s="5">
         <v>259</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E151" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>305</v>
       </c>
@@ -5212,8 +5681,11 @@
       <c r="D152" s="5">
         <v>476</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E152" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>307</v>
       </c>
@@ -5226,8 +5698,11 @@
       <c r="D153" s="5">
         <v>158</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E153" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>309</v>
       </c>
@@ -5240,8 +5715,11 @@
       <c r="D154" s="5">
         <v>158</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E154" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>311</v>
       </c>
@@ -5254,8 +5732,11 @@
       <c r="D155" s="5">
         <v>158</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E155" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>313</v>
       </c>
@@ -5268,8 +5749,11 @@
       <c r="D156" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E156" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>315</v>
       </c>
@@ -5282,8 +5766,11 @@
       <c r="D157" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E157" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>317</v>
       </c>
@@ -5296,8 +5783,11 @@
       <c r="D158" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E158" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>319</v>
       </c>
@@ -5310,8 +5800,11 @@
       <c r="D159" s="5">
         <v>298</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E159" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>321</v>
       </c>
@@ -5324,8 +5817,11 @@
       <c r="D160" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E160" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>323</v>
       </c>
@@ -5338,8 +5834,11 @@
       <c r="D161" s="5">
         <v>198</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E161" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>325</v>
       </c>
@@ -5352,8 +5851,11 @@
       <c r="D162" s="5">
         <v>148</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E162" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>327</v>
       </c>
@@ -5366,8 +5868,11 @@
       <c r="D163" s="5">
         <v>780</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E163" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>329</v>
       </c>
@@ -5380,8 +5885,11 @@
       <c r="D164" s="5">
         <v>490</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E164" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>331</v>
       </c>
@@ -5394,8 +5902,11 @@
       <c r="D165" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E165" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>333</v>
       </c>
@@ -5408,8 +5919,11 @@
       <c r="D166" s="5">
         <v>211</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E166" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>335</v>
       </c>
@@ -5422,8 +5936,11 @@
       <c r="D167" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E167" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>337</v>
       </c>
@@ -5436,8 +5953,11 @@
       <c r="D168" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E168" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>339</v>
       </c>
@@ -5450,8 +5970,11 @@
       <c r="D169" s="5">
         <v>158.51</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E169" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>341</v>
       </c>
@@ -5464,8 +5987,11 @@
       <c r="D170" s="5">
         <v>398</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E170" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>343</v>
       </c>
@@ -5478,8 +6004,11 @@
       <c r="D171" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E171" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>345</v>
       </c>
@@ -5492,8 +6021,11 @@
       <c r="D172" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E172" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>347</v>
       </c>
@@ -5506,8 +6038,11 @@
       <c r="D173" s="5">
         <v>180</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E173" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>349</v>
       </c>
@@ -5520,8 +6055,11 @@
       <c r="D174" s="5">
         <v>288</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E174" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>351</v>
       </c>
@@ -5534,8 +6072,11 @@
       <c r="D175" s="5">
         <v>424</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E175" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>353</v>
       </c>
@@ -5548,8 +6089,11 @@
       <c r="D176" s="5">
         <v>147.87</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E176" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>355</v>
       </c>
@@ -5562,8 +6106,11 @@
       <c r="D177" s="5">
         <v>186</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E177" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>357</v>
       </c>
@@ -5576,8 +6123,11 @@
       <c r="D178" s="5">
         <v>202.13</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E178" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>359</v>
       </c>
@@ -5590,8 +6140,11 @@
       <c r="D179" s="5">
         <v>153</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E179" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>361</v>
       </c>
@@ -5604,8 +6157,11 @@
       <c r="D180" s="5">
         <v>50</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E180" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>363</v>
       </c>
@@ -5618,8 +6174,11 @@
       <c r="D181" s="5">
         <v>50</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E181" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>365</v>
       </c>
@@ -5632,8 +6191,11 @@
       <c r="D182" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E182" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>367</v>
       </c>
@@ -5646,8 +6208,11 @@
       <c r="D183" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E183" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>369</v>
       </c>
@@ -5660,8 +6225,11 @@
       <c r="D184" s="5">
         <v>201.06</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E184" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>371</v>
       </c>
@@ -5674,8 +6242,11 @@
       <c r="D185" s="5">
         <v>1042.55</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E185" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>373</v>
       </c>
@@ -5688,8 +6259,11 @@
       <c r="D186" s="5">
         <v>339.36</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E186" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>375</v>
       </c>
@@ -5702,8 +6276,11 @@
       <c r="D187" s="5">
         <v>425</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E187" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>377</v>
       </c>
@@ -5716,8 +6293,11 @@
       <c r="D188" s="5">
         <v>1100</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E188" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>379</v>
       </c>
@@ -5730,8 +6310,11 @@
       <c r="D189" s="5">
         <v>510</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E189" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>381</v>
       </c>
@@ -5744,8 +6327,11 @@
       <c r="D190" s="5">
         <v>850</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E190" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>383</v>
       </c>
@@ -5758,8 +6344,11 @@
       <c r="D191" s="5">
         <v>890</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E191" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>385</v>
       </c>
@@ -5772,8 +6361,11 @@
       <c r="D192" s="5">
         <v>617.02</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E192" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>387</v>
       </c>
@@ -5786,8 +6378,11 @@
       <c r="D193" s="5">
         <v>68</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E193" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>389</v>
       </c>
@@ -5800,8 +6395,11 @@
       <c r="D194" s="5">
         <v>164</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E194" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>391</v>
       </c>
@@ -5814,8 +6412,11 @@
       <c r="D195" s="5">
         <v>290</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E195" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>393</v>
       </c>
@@ -5828,8 +6429,11 @@
       <c r="D196" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E196" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>395</v>
       </c>
@@ -5842,8 +6446,11 @@
       <c r="D197" s="5">
         <v>148</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E197" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>397</v>
       </c>
@@ -5856,8 +6463,11 @@
       <c r="D198" s="5">
         <v>266</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E198" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>399</v>
       </c>
@@ -5870,8 +6480,11 @@
       <c r="D199" s="5">
         <v>162</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E199" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>401</v>
       </c>
@@ -5884,8 +6497,11 @@
       <c r="D200" s="5">
         <v>410</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E200" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>403</v>
       </c>
@@ -5898,8 +6514,11 @@
       <c r="D201" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E201" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>405</v>
       </c>
@@ -5912,8 +6531,11 @@
       <c r="D202" s="5">
         <v>750</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E202" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>407</v>
       </c>
@@ -5926,8 +6548,11 @@
       <c r="D203" s="5">
         <v>37.229999999999997</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E203" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>409</v>
       </c>
@@ -5940,8 +6565,11 @@
       <c r="D204" s="5">
         <v>47.87</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E204" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>411</v>
       </c>
@@ -5954,8 +6582,11 @@
       <c r="D205" s="5">
         <v>450</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E205" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>413</v>
       </c>
@@ -5968,8 +6599,11 @@
       <c r="D206" s="5">
         <v>590</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E206" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>415</v>
       </c>
@@ -5982,8 +6616,11 @@
       <c r="D207" s="5">
         <v>260</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E207" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>417</v>
       </c>
@@ -5996,8 +6633,11 @@
       <c r="D208" s="5">
         <v>300</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E208" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>419</v>
       </c>
@@ -6010,8 +6650,11 @@
       <c r="D209" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E209" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>421</v>
       </c>
@@ -6024,8 +6667,11 @@
       <c r="D210" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E210" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>423</v>
       </c>
@@ -6038,8 +6684,11 @@
       <c r="D211" s="5">
         <v>45</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E211" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>425</v>
       </c>
@@ -6052,8 +6701,11 @@
       <c r="D212" s="5">
         <v>250</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E212" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>427</v>
       </c>
@@ -6066,8 +6718,11 @@
       <c r="D213" s="5">
         <v>168</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E213" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>429</v>
       </c>
@@ -6080,8 +6735,11 @@
       <c r="D214" s="5">
         <v>250</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E214" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>431</v>
       </c>
@@ -6094,8 +6752,11 @@
       <c r="D215" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E215" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>433</v>
       </c>
@@ -6108,8 +6769,11 @@
       <c r="D216" s="5">
         <v>260.64</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E216" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>435</v>
       </c>
@@ -6122,8 +6786,11 @@
       <c r="D217" s="5">
         <v>1190</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E217" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>437</v>
       </c>
@@ -6136,8 +6803,11 @@
       <c r="D218" s="5">
         <v>2328.7199999999998</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E218" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>439</v>
       </c>
@@ -6150,8 +6820,11 @@
       <c r="D219" s="5">
         <v>2760</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E219" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>441</v>
       </c>
@@ -6164,8 +6837,11 @@
       <c r="D220" s="5">
         <v>820</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E220" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>443</v>
       </c>
@@ -6178,8 +6854,11 @@
       <c r="D221" s="5">
         <v>827.66</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E221" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>445</v>
       </c>
@@ -6192,8 +6871,11 @@
       <c r="D222" s="5">
         <v>732.98</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E222" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>447</v>
       </c>
@@ -6206,8 +6888,11 @@
       <c r="D223" s="5">
         <v>790.43</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E223" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>449</v>
       </c>
@@ -6220,8 +6905,11 @@
       <c r="D224" s="5">
         <v>1117.02</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E224" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>451</v>
       </c>
@@ -6234,8 +6922,11 @@
       <c r="D225" s="5">
         <v>775.53</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E225" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>453</v>
       </c>
@@ -6248,8 +6939,11 @@
       <c r="D226" s="5">
         <v>1690</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E226" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>455</v>
       </c>
@@ -6262,8 +6956,11 @@
       <c r="D227" s="5">
         <v>2989</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E227" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>457</v>
       </c>
@@ -6276,8 +6973,11 @@
       <c r="D228" s="5">
         <v>1690</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E228" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>459</v>
       </c>
@@ -6290,8 +6990,11 @@
       <c r="D229" s="5">
         <v>3700</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E229" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>461</v>
       </c>
@@ -6304,8 +7007,11 @@
       <c r="D230" s="5">
         <v>1806</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E230" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>463</v>
       </c>
@@ -6318,8 +7024,11 @@
       <c r="D231" s="5">
         <v>1990</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E231" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>465</v>
       </c>
@@ -6332,8 +7041,11 @@
       <c r="D232" s="5">
         <v>6002.13</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E232" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>467</v>
       </c>
@@ -6346,8 +7058,11 @@
       <c r="D233" s="5">
         <v>4138.3</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E233" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>469</v>
       </c>
@@ -6360,8 +7075,11 @@
       <c r="D234" s="5">
         <v>4000</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E234" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>471</v>
       </c>
@@ -6374,8 +7092,11 @@
       <c r="D235" s="5">
         <v>6777.1</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E235" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>473</v>
       </c>
@@ -6388,8 +7109,11 @@
       <c r="D236" s="5">
         <v>6159.57</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E236" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>475</v>
       </c>
@@ -6402,8 +7126,11 @@
       <c r="D237" s="5">
         <v>4600</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E237" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>477</v>
       </c>
@@ -6416,8 +7143,11 @@
       <c r="D238" s="5">
         <v>1170.21</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E238" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>479</v>
       </c>
@@ -6430,8 +7160,11 @@
       <c r="D239" s="5">
         <v>1350</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E239" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>481</v>
       </c>
@@ -6444,8 +7177,11 @@
       <c r="D240" s="5">
         <v>849</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E240" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>483</v>
       </c>
@@ -6458,8 +7194,11 @@
       <c r="D241" s="5">
         <v>1050</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E241" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>485</v>
       </c>
@@ -6472,8 +7211,11 @@
       <c r="D242" s="5">
         <v>2100</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E242" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>487</v>
       </c>
@@ -6486,8 +7228,11 @@
       <c r="D243" s="5">
         <v>848</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E243" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>489</v>
       </c>
@@ -6500,8 +7245,11 @@
       <c r="D244" s="5">
         <v>637</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E244" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>491</v>
       </c>
@@ -6514,8 +7262,11 @@
       <c r="D245" s="5">
         <v>500</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E245" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>493</v>
       </c>
@@ -6528,8 +7279,11 @@
       <c r="D246" s="5">
         <v>500</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E246" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>495</v>
       </c>
@@ -6542,8 +7296,11 @@
       <c r="D247" s="5">
         <v>478.72</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E247" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>497</v>
       </c>
@@ -6556,8 +7313,11 @@
       <c r="D248" s="5">
         <v>478.72</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E248" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>499</v>
       </c>
@@ -6570,8 +7330,11 @@
       <c r="D249" s="5">
         <v>930</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E249" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>501</v>
       </c>
@@ -6584,8 +7347,11 @@
       <c r="D250" s="5">
         <v>39</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E250" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>503</v>
       </c>
@@ -6598,8 +7364,11 @@
       <c r="D251" s="5">
         <v>8917.02</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E251" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>505</v>
       </c>
@@ -6612,8 +7381,11 @@
       <c r="D252" s="5">
         <v>14787.23</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E252" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>507</v>
       </c>
@@ -6626,8 +7398,11 @@
       <c r="D253" s="5">
         <v>12900</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E253" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>509</v>
       </c>
@@ -6640,8 +7415,11 @@
       <c r="D254" s="5">
         <v>14000</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E254" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>511</v>
       </c>
@@ -6654,8 +7432,11 @@
       <c r="D255" s="5">
         <v>20000</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E255" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>513</v>
       </c>
@@ -6668,8 +7449,11 @@
       <c r="D256" s="5">
         <v>19800</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E256" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>515</v>
       </c>
@@ -6682,8 +7466,11 @@
       <c r="D257" s="5">
         <v>9500</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E257" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>517</v>
       </c>
@@ -6696,8 +7483,11 @@
       <c r="D258" s="5">
         <v>14600</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E258" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>519</v>
       </c>
@@ -6710,8 +7500,11 @@
       <c r="D259" s="5">
         <v>21100</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E259" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>521</v>
       </c>
@@ -6724,8 +7517,11 @@
       <c r="D260" s="5">
         <v>18000</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E260" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>523</v>
       </c>
@@ -6738,8 +7534,11 @@
       <c r="D261" s="5">
         <v>5500</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E261" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>525</v>
       </c>
@@ -6752,8 +7551,11 @@
       <c r="D262" s="5">
         <v>560</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E262" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>527</v>
       </c>
@@ -6766,8 +7568,11 @@
       <c r="D263" s="5">
         <v>4457.45</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E263" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>529</v>
       </c>
@@ -6780,8 +7585,11 @@
       <c r="D264" s="5">
         <v>10300</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E264" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>531</v>
       </c>
@@ -6794,8 +7602,11 @@
       <c r="D265" s="5">
         <v>10900</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E265" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>533</v>
       </c>
@@ -6808,8 +7619,11 @@
       <c r="D266" s="5">
         <v>11200</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E266" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>534</v>
       </c>
@@ -6822,8 +7636,11 @@
       <c r="D267" s="5">
         <v>10521.28</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E267" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>536</v>
       </c>
@@ -6836,8 +7653,11 @@
       <c r="D268" s="5">
         <v>6361.7</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E268" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>538</v>
       </c>
@@ -6850,8 +7670,11 @@
       <c r="D269" s="5">
         <v>4978.72</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E269" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>540</v>
       </c>
@@ -6864,8 +7687,11 @@
       <c r="D270" s="5">
         <v>5531.91</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E270" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>542</v>
       </c>
@@ -6878,8 +7704,11 @@
       <c r="D271" s="5">
         <v>3936.17</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E271" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>544</v>
       </c>
@@ -6892,8 +7721,11 @@
       <c r="D272" s="5">
         <v>2000</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E272" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>546</v>
       </c>
@@ -6906,8 +7738,11 @@
       <c r="D273" s="5">
         <v>4800</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E273" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>548</v>
       </c>
@@ -6920,8 +7755,11 @@
       <c r="D274" s="5">
         <v>3800</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E274" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>550</v>
       </c>
@@ -6934,8 +7772,11 @@
       <c r="D275" s="5">
         <v>318</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E275" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>552</v>
       </c>
@@ -6948,8 +7789,11 @@
       <c r="D276" s="5">
         <v>1790</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E276" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>554</v>
       </c>
@@ -6962,8 +7806,11 @@
       <c r="D277" s="5">
         <v>410</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E277" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>556</v>
       </c>
@@ -6976,8 +7823,11 @@
       <c r="D278" s="5">
         <v>3700</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E278" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>558</v>
       </c>
@@ -6990,8 +7840,11 @@
       <c r="D279" s="5">
         <v>890</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E279" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>560</v>
       </c>
@@ -7004,8 +7857,11 @@
       <c r="D280" s="5">
         <v>410</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E280" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>562</v>
       </c>
@@ -7018,8 +7874,11 @@
       <c r="D281" s="5">
         <v>890</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E281" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>564</v>
       </c>
@@ -7032,8 +7891,11 @@
       <c r="D282" s="5">
         <v>340</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E282" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>566</v>
       </c>
@@ -7046,8 +7908,11 @@
       <c r="D283" s="5">
         <v>310</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E283" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>568</v>
       </c>
@@ -7060,8 +7925,11 @@
       <c r="D284" s="5">
         <v>614.89</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E284" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>570</v>
       </c>
@@ -7074,8 +7942,11 @@
       <c r="D285" s="5">
         <v>3300</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E285" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>572</v>
       </c>
@@ -7088,8 +7959,11 @@
       <c r="D286" s="5">
         <v>3000</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E286" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>574</v>
       </c>
@@ -7102,8 +7976,11 @@
       <c r="D287" s="5">
         <v>318</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E287" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>576</v>
       </c>
@@ -7116,8 +7993,11 @@
       <c r="D288" s="5">
         <v>192</v>
       </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E288" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>578</v>
       </c>
@@ -7130,8 +8010,11 @@
       <c r="D289" s="5">
         <v>39</v>
       </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E289" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>580</v>
       </c>
@@ -7144,8 +8027,11 @@
       <c r="D290" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E290" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>582</v>
       </c>
@@ -7158,8 +8044,11 @@
       <c r="D291" s="5">
         <v>1050</v>
       </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E291" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>584</v>
       </c>
@@ -7172,8 +8061,11 @@
       <c r="D292" s="5">
         <v>510.64</v>
       </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E292" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>586</v>
       </c>
@@ -7186,8 +8078,11 @@
       <c r="D293" s="5">
         <v>1100</v>
       </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E293" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>588</v>
       </c>
@@ -7200,8 +8095,11 @@
       <c r="D294" s="5">
         <v>168</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E294" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>590</v>
       </c>
@@ -7214,8 +8112,11 @@
       <c r="D295" s="5">
         <v>200</v>
       </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E295" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>592</v>
       </c>
@@ -7228,8 +8129,11 @@
       <c r="D296" s="5">
         <v>69</v>
       </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E296" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>594</v>
       </c>
@@ -7242,8 +8146,11 @@
       <c r="D297" s="5">
         <v>106</v>
       </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E297" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>596</v>
       </c>
@@ -7256,8 +8163,11 @@
       <c r="D298" s="5">
         <v>79</v>
       </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E298" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>598</v>
       </c>
@@ -7270,8 +8180,11 @@
       <c r="D299" s="5">
         <v>360</v>
       </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E299" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>600</v>
       </c>
@@ -7284,8 +8197,11 @@
       <c r="D300" s="5">
         <v>780</v>
       </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E300" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>602</v>
       </c>
@@ -7298,8 +8214,11 @@
       <c r="D301" s="5">
         <v>296.67</v>
       </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E301" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>604</v>
       </c>
@@ -7312,8 +8231,11 @@
       <c r="D302" s="5">
         <v>1380</v>
       </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E302" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>606</v>
       </c>
@@ -7326,8 +8248,11 @@
       <c r="D303" s="5">
         <v>160</v>
       </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E303" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>608</v>
       </c>
@@ -7340,8 +8265,11 @@
       <c r="D304" s="5">
         <v>95</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E304" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>610</v>
       </c>
@@ -7354,8 +8282,11 @@
       <c r="D305" s="5">
         <v>70</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E305" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>612</v>
       </c>
@@ -7368,8 +8299,11 @@
       <c r="D306" s="5">
         <v>180</v>
       </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E306" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>614</v>
       </c>
@@ -7382,8 +8316,11 @@
       <c r="D307" s="5">
         <v>120</v>
       </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E307" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>616</v>
       </c>
@@ -7396,8 +8333,11 @@
       <c r="D308" s="5">
         <v>179</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E308" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>618</v>
       </c>
@@ -7410,8 +8350,11 @@
       <c r="D309" s="5">
         <v>179</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E309" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>620</v>
       </c>
@@ -7424,8 +8367,11 @@
       <c r="D310" s="5">
         <v>74</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E310" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>622</v>
       </c>
@@ -7438,8 +8384,11 @@
       <c r="D311" s="5">
         <v>79</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E311" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>624</v>
       </c>
@@ -7452,8 +8401,11 @@
       <c r="D312" s="5">
         <v>198</v>
       </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E312" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>626</v>
       </c>
@@ -7466,8 +8418,11 @@
       <c r="D313" s="5">
         <v>197.87</v>
       </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E313" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>628</v>
       </c>
@@ -7480,8 +8435,11 @@
       <c r="D314" s="5">
         <v>5900</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E314" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>630</v>
       </c>
@@ -7494,8 +8452,11 @@
       <c r="D315" s="5">
         <v>5800</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E315" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>632</v>
       </c>
@@ -7508,8 +8469,11 @@
       <c r="D316" s="5">
         <v>8430</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E316" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>634</v>
       </c>
@@ -7522,8 +8486,11 @@
       <c r="D317" s="5">
         <v>11600</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E317" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>636</v>
       </c>
@@ -7536,8 +8503,11 @@
       <c r="D318" s="5">
         <v>5980</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E318" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>638</v>
       </c>
@@ -7550,8 +8520,11 @@
       <c r="D319" s="5">
         <v>6300</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E319" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>640</v>
       </c>
@@ -7564,8 +8537,11 @@
       <c r="D320" s="5">
         <v>4890</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E320" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>642</v>
       </c>
@@ -7578,8 +8554,11 @@
       <c r="D321" s="5">
         <v>4890</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E321" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>644</v>
       </c>
@@ -7592,8 +8571,11 @@
       <c r="D322" s="5">
         <v>460</v>
       </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E322" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>646</v>
       </c>
@@ -7606,8 +8588,11 @@
       <c r="D323" s="5">
         <v>848.94</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E323" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>648</v>
       </c>
@@ -7620,8 +8605,11 @@
       <c r="D324" s="5">
         <v>1190</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E324" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>650</v>
       </c>
@@ -7634,8 +8622,11 @@
       <c r="D325" s="5">
         <v>125.53</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E325" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>652</v>
       </c>
@@ -7648,8 +8639,11 @@
       <c r="D326" s="5">
         <v>530</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E326" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>654</v>
       </c>
@@ -7662,8 +8656,11 @@
       <c r="D327" s="5">
         <v>470</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E327" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>656</v>
       </c>
@@ -7676,8 +8673,11 @@
       <c r="D328" s="5">
         <v>284</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E328" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>658</v>
       </c>
@@ -7690,8 +8690,11 @@
       <c r="D329" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E329" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>660</v>
       </c>
@@ -7704,8 +8707,11 @@
       <c r="D330" s="5">
         <v>210.64</v>
       </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E330" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>662</v>
       </c>
@@ -7718,8 +8724,11 @@
       <c r="D331" s="5">
         <v>228.72</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E331" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>664</v>
       </c>
@@ -7732,8 +8741,11 @@
       <c r="D332" s="5">
         <v>126</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E332" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>666</v>
       </c>
@@ -7746,8 +8758,11 @@
       <c r="D333" s="5">
         <v>169</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E333" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>668</v>
       </c>
@@ -7760,8 +8775,11 @@
       <c r="D334" s="5">
         <v>169</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E334" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>670</v>
       </c>
@@ -7774,8 +8792,11 @@
       <c r="D335" s="5">
         <v>2800</v>
       </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E335" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>672</v>
       </c>
@@ -7788,8 +8809,11 @@
       <c r="D336" s="5">
         <v>279</v>
       </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E336" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>674</v>
       </c>
@@ -7802,8 +8826,11 @@
       <c r="D337" s="5">
         <v>2120</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E337" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>676</v>
       </c>
@@ -7816,8 +8843,11 @@
       <c r="D338" s="5">
         <v>1590</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E338" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>678</v>
       </c>
@@ -7830,8 +8860,11 @@
       <c r="D339" s="5">
         <v>356.38</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E339" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>680</v>
       </c>
@@ -7844,8 +8877,11 @@
       <c r="D340" s="5">
         <v>230</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E340" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>682</v>
       </c>
@@ -7858,8 +8894,11 @@
       <c r="D341" s="5">
         <v>485</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E341" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>684</v>
       </c>
@@ -7872,8 +8911,11 @@
       <c r="D342" s="5">
         <v>420</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E342" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>686</v>
       </c>
@@ -7886,8 +8928,11 @@
       <c r="D343" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E343" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>688</v>
       </c>
@@ -7900,8 +8945,11 @@
       <c r="D344" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E344" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>690</v>
       </c>
@@ -7914,8 +8962,11 @@
       <c r="D345" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E345" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>692</v>
       </c>
@@ -7928,8 +8979,11 @@
       <c r="D346" s="5">
         <v>780</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E346" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>694</v>
       </c>
@@ -7942,8 +8996,11 @@
       <c r="D347" s="5">
         <v>780</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E347" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>696</v>
       </c>
@@ -7956,8 +9013,11 @@
       <c r="D348" s="5">
         <v>760</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E348" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>698</v>
       </c>
@@ -7970,8 +9030,11 @@
       <c r="D349" s="5">
         <v>160</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E349" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>700</v>
       </c>
@@ -7984,8 +9047,11 @@
       <c r="D350" s="5">
         <v>178.72</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E350" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>702</v>
       </c>
@@ -7998,8 +9064,11 @@
       <c r="D351" s="5">
         <v>420</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E351" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>704</v>
       </c>
@@ -8012,8 +9081,11 @@
       <c r="D352" s="5">
         <v>690</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E352" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>706</v>
       </c>
@@ -8026,8 +9098,11 @@
       <c r="D353" s="5">
         <v>360</v>
       </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E353" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>708</v>
       </c>
@@ -8040,8 +9115,11 @@
       <c r="D354" s="5">
         <v>690</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E354" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>710</v>
       </c>
@@ -8054,8 +9132,11 @@
       <c r="D355" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E355" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>712</v>
       </c>
@@ -8068,8 +9149,11 @@
       <c r="D356" s="5">
         <v>35</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E356" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>714</v>
       </c>
@@ -8082,8 +9166,11 @@
       <c r="D357" s="5">
         <v>350</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E357" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>716</v>
       </c>
@@ -8096,8 +9183,11 @@
       <c r="D358" s="5">
         <v>1913</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E358" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>718</v>
       </c>
@@ -8110,8 +9200,11 @@
       <c r="D359" s="5">
         <v>620</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E359" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>720</v>
       </c>
@@ -8124,8 +9217,11 @@
       <c r="D360" s="5">
         <v>360</v>
       </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E360" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>722</v>
       </c>
@@ -8138,8 +9234,11 @@
       <c r="D361" s="5">
         <v>1780</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E361" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>724</v>
       </c>
@@ -8152,8 +9251,11 @@
       <c r="D362" s="5">
         <v>320</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E362" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>726</v>
       </c>
@@ -8166,8 +9268,11 @@
       <c r="D363" s="5">
         <v>1060</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E363" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>728</v>
       </c>
@@ -8180,8 +9285,11 @@
       <c r="D364" s="5">
         <v>310</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E364" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>730</v>
       </c>
@@ -8194,8 +9302,11 @@
       <c r="D365" s="5">
         <v>530</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E365" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>732</v>
       </c>
@@ -8208,8 +9319,11 @@
       <c r="D366" s="5">
         <v>830</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E366" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>734</v>
       </c>
@@ -8222,8 +9336,11 @@
       <c r="D367" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E367" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>736</v>
       </c>
@@ -8236,8 +9353,11 @@
       <c r="D368" s="5">
         <v>300</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E368" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>738</v>
       </c>
@@ -8250,8 +9370,11 @@
       <c r="D369" s="5">
         <v>85.11</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E369" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>740</v>
       </c>
@@ -8264,8 +9387,11 @@
       <c r="D370" s="5">
         <v>70</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E370" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>742</v>
       </c>
@@ -8278,8 +9404,11 @@
       <c r="D371" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E371" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>744</v>
       </c>
@@ -8292,8 +9421,11 @@
       <c r="D372" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E372" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>746</v>
       </c>
@@ -8306,8 +9438,11 @@
       <c r="D373" s="5">
         <v>420</v>
       </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E373" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>748</v>
       </c>
@@ -8320,8 +9455,11 @@
       <c r="D374" s="5">
         <v>290</v>
       </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E374" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>750</v>
       </c>
@@ -8334,8 +9472,11 @@
       <c r="D375" s="5">
         <v>740</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E375" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>752</v>
       </c>
@@ -8348,8 +9489,11 @@
       <c r="D376" s="5">
         <v>848</v>
       </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E376" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>754</v>
       </c>
@@ -8362,8 +9506,11 @@
       <c r="D377" s="5">
         <v>780</v>
       </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E377" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>756</v>
       </c>
@@ -8376,8 +9523,11 @@
       <c r="D378" s="5">
         <v>300</v>
       </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E378" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>758</v>
       </c>
@@ -8390,8 +9540,11 @@
       <c r="D379" s="5">
         <v>1680</v>
       </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E379" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>760</v>
       </c>
@@ -8404,8 +9557,11 @@
       <c r="D380" s="5">
         <v>530</v>
       </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E380" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>762</v>
       </c>
@@ -8418,8 +9574,11 @@
       <c r="D381" s="5">
         <v>49</v>
       </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E381" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>764</v>
       </c>
@@ -8432,8 +9591,11 @@
       <c r="D382" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E382" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>766</v>
       </c>
@@ -8446,8 +9608,11 @@
       <c r="D383" s="5">
         <v>290</v>
       </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E383" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>768</v>
       </c>
@@ -8460,8 +9625,11 @@
       <c r="D384" s="5">
         <v>1500</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E384" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>770</v>
       </c>
@@ -8474,8 +9642,11 @@
       <c r="D385" s="5">
         <v>1042.55</v>
       </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E385" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>772</v>
       </c>
@@ -8488,8 +9659,11 @@
       <c r="D386" s="5">
         <v>480</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E386" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>774</v>
       </c>
@@ -8502,8 +9676,11 @@
       <c r="D387" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E387" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>776</v>
       </c>
@@ -8516,8 +9693,11 @@
       <c r="D388" s="5">
         <v>2234.04</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E388" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>778</v>
       </c>
@@ -8530,8 +9710,11 @@
       <c r="D389" s="5">
         <v>670</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E389" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>780</v>
       </c>
@@ -8544,8 +9727,11 @@
       <c r="D390" s="5">
         <v>510.64</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E390" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>782</v>
       </c>
@@ -8558,8 +9744,11 @@
       <c r="D391" s="5">
         <v>480</v>
       </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E391" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>784</v>
       </c>
@@ -8572,8 +9761,11 @@
       <c r="D392" s="5">
         <v>690</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E392" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>786</v>
       </c>
@@ -8586,8 +9778,11 @@
       <c r="D393" s="5">
         <v>234.04</v>
       </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E393" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>788</v>
       </c>
@@ -8600,8 +9795,11 @@
       <c r="D394" s="5">
         <v>130</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E394" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>790</v>
       </c>
@@ -8614,8 +9812,11 @@
       <c r="D395" s="5">
         <v>78</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E395" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>792</v>
       </c>
@@ -8628,8 +9829,11 @@
       <c r="D396" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E396" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>794</v>
       </c>
@@ -8642,8 +9846,11 @@
       <c r="D397" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E397" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>796</v>
       </c>
@@ -8656,8 +9863,11 @@
       <c r="D398" s="5">
         <v>3800</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E398" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>798</v>
       </c>
@@ -8670,8 +9880,11 @@
       <c r="D399" s="5">
         <v>4200</v>
       </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E399" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>800</v>
       </c>
@@ -8684,8 +9897,11 @@
       <c r="D400" s="5">
         <v>1100</v>
       </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E400" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>802</v>
       </c>
@@ -8698,8 +9914,11 @@
       <c r="D401" s="5">
         <v>6050</v>
       </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E401" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>804</v>
       </c>
@@ -8712,8 +9931,11 @@
       <c r="D402" s="5">
         <v>9800</v>
       </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E402" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>806</v>
       </c>
@@ -8726,8 +9948,11 @@
       <c r="D403" s="5">
         <v>2861.7</v>
       </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E403" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>808</v>
       </c>
@@ -8740,8 +9965,11 @@
       <c r="D404" s="5">
         <v>6990</v>
       </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E404" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>810</v>
       </c>
@@ -8754,8 +9982,11 @@
       <c r="D405" s="5">
         <v>12670</v>
       </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E405" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>812</v>
       </c>
@@ -8768,8 +9999,11 @@
       <c r="D406" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E406" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>814</v>
       </c>
@@ -8782,8 +10016,11 @@
       <c r="D407" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E407" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>816</v>
       </c>
@@ -8796,8 +10033,11 @@
       <c r="D408" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E408" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>818</v>
       </c>
@@ -8810,8 +10050,11 @@
       <c r="D409" s="5">
         <v>790</v>
       </c>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E409" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>819</v>
       </c>
@@ -8824,8 +10067,11 @@
       <c r="D410" s="5">
         <v>510</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E410" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>821</v>
       </c>
@@ -8838,8 +10084,11 @@
       <c r="D411" s="5">
         <v>10406</v>
       </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E411" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>823</v>
       </c>
@@ -8852,8 +10101,11 @@
       <c r="D412" s="5">
         <v>617.02</v>
       </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E412" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>825</v>
       </c>
@@ -8866,8 +10118,11 @@
       <c r="D413" s="5">
         <v>423.4</v>
       </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E413" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>827</v>
       </c>
@@ -8880,8 +10135,11 @@
       <c r="D414" s="5">
         <v>423.4</v>
       </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E414" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>829</v>
       </c>
@@ -8894,8 +10152,11 @@
       <c r="D415" s="5">
         <v>210</v>
       </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E415" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>831</v>
       </c>
@@ -8908,8 +10169,11 @@
       <c r="D416" s="5">
         <v>318</v>
       </c>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E416" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>833</v>
       </c>
@@ -8922,8 +10186,11 @@
       <c r="D417" s="5">
         <v>190.42</v>
       </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E417" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>835</v>
       </c>
@@ -8936,8 +10203,11 @@
       <c r="D418" s="5">
         <v>13900</v>
       </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E418" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>837</v>
       </c>
@@ -8950,8 +10220,11 @@
       <c r="D419" s="5">
         <v>848</v>
       </c>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E419" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>839</v>
       </c>
@@ -8964,8 +10237,11 @@
       <c r="D420" s="5">
         <v>10521.28</v>
       </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E420" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>841</v>
       </c>
@@ -8978,8 +10254,11 @@
       <c r="D421" s="5">
         <v>840.42</v>
       </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E421" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>843</v>
       </c>
@@ -8992,8 +10271,11 @@
       <c r="D422" s="5">
         <v>296.67</v>
       </c>
-    </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E422" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>845</v>
       </c>
@@ -9006,8 +10288,11 @@
       <c r="D423" s="5">
         <v>128</v>
       </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E423" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>847</v>
       </c>
@@ -9020,8 +10305,11 @@
       <c r="D424" s="5">
         <v>128</v>
       </c>
-    </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E424" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>849</v>
       </c>
@@ -9034,8 +10322,11 @@
       <c r="D425" s="5">
         <v>16914.89</v>
       </c>
-    </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E425" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>851</v>
       </c>
@@ -9048,8 +10339,11 @@
       <c r="D426" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E426" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>853</v>
       </c>
@@ -9062,8 +10356,11 @@
       <c r="D427" s="5">
         <v>520</v>
       </c>
-    </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E427" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>855</v>
       </c>
@@ -9076,8 +10373,11 @@
       <c r="D428" s="5">
         <v>480</v>
       </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E428" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>857</v>
       </c>
@@ -9090,8 +10390,11 @@
       <c r="D429" s="5">
         <v>1042.55</v>
       </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E429" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>859</v>
       </c>
@@ -9104,8 +10407,11 @@
       <c r="D430" s="5">
         <v>1398.94</v>
       </c>
-    </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E430" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>861</v>
       </c>
@@ -9118,8 +10424,11 @@
       <c r="D431" s="5">
         <v>742</v>
       </c>
-    </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E431" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>863</v>
       </c>
@@ -9132,8 +10441,11 @@
       <c r="D432" s="5">
         <v>458</v>
       </c>
-    </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E432" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>865</v>
       </c>
@@ -9146,8 +10458,11 @@
       <c r="D433" s="5">
         <v>580</v>
       </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E433" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>867</v>
       </c>
@@ -9160,8 +10475,11 @@
       <c r="D434" s="5">
         <v>580</v>
       </c>
-    </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E434" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>869</v>
       </c>
@@ -9174,8 +10492,11 @@
       <c r="D435" s="5">
         <v>742.55</v>
       </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E435" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>871</v>
       </c>
@@ -9187,6 +10508,9 @@
       </c>
       <c r="D436" s="5">
         <v>197</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>876</v>
       </c>
     </row>
   </sheetData>
